--- a/data/nzd0142/nzd0142.xlsx
+++ b/data/nzd0142/nzd0142.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G316"/>
+  <dimension ref="A1:G317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8970,6 +8970,33 @@
       <c r="G316" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>359.81</v>
+      </c>
+      <c r="C317" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="D317" t="n">
+        <v>357.07</v>
+      </c>
+      <c r="E317" t="n">
+        <v>354.38</v>
+      </c>
+      <c r="F317" t="n">
+        <v>369.46</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8984,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B334"/>
+  <dimension ref="A1:B335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12327,6 +12354,16 @@
       </c>
       <c r="B334" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -12495,28 +12532,28 @@
         <v>0.0985</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1306285642454906</v>
+        <v>0.1279518840039161</v>
       </c>
       <c r="J2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0614941139493228</v>
+        <v>0.05927874278549738</v>
       </c>
       <c r="M2" t="n">
-        <v>2.951855979239197</v>
+        <v>2.955147020259369</v>
       </c>
       <c r="N2" t="n">
-        <v>13.91947987168505</v>
+        <v>13.93382616567677</v>
       </c>
       <c r="O2" t="n">
-        <v>3.730881916073605</v>
+        <v>3.732804062052651</v>
       </c>
       <c r="P2" t="n">
-        <v>360.7161606876747</v>
+        <v>360.7442548823154</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12573,28 +12610,28 @@
         <v>0.129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1561177150959115</v>
+        <v>0.1507849586246411</v>
       </c>
       <c r="J3" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K3" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04984641818209545</v>
+        <v>0.04653269174496755</v>
       </c>
       <c r="M3" t="n">
-        <v>4.080295180340043</v>
+        <v>4.091319693203132</v>
       </c>
       <c r="N3" t="n">
-        <v>24.8317583879489</v>
+        <v>24.98496344398242</v>
       </c>
       <c r="O3" t="n">
-        <v>4.98314743790999</v>
+        <v>4.998496118232205</v>
       </c>
       <c r="P3" t="n">
-        <v>364.0769458900253</v>
+        <v>364.1329180214547</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12651,28 +12688,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3071544549967574</v>
+        <v>0.3009444950726503</v>
       </c>
       <c r="J4" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K4" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1418122574494881</v>
+        <v>0.1364740136415055</v>
       </c>
       <c r="M4" t="n">
-        <v>4.423649557858739</v>
+        <v>4.439191909243849</v>
       </c>
       <c r="N4" t="n">
-        <v>30.51584653658351</v>
+        <v>30.73359041425964</v>
       </c>
       <c r="O4" t="n">
-        <v>5.524115000303986</v>
+        <v>5.54378845323842</v>
       </c>
       <c r="P4" t="n">
-        <v>359.0625914405009</v>
+        <v>359.1277706203334</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12729,28 +12766,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3584584979880275</v>
+        <v>0.3500573439386048</v>
       </c>
       <c r="J5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1416119100419274</v>
+        <v>0.1350990948578301</v>
       </c>
       <c r="M5" t="n">
-        <v>5.280735458165848</v>
+        <v>5.301547109153518</v>
       </c>
       <c r="N5" t="n">
-        <v>41.62985631304703</v>
+        <v>42.07337425539114</v>
       </c>
       <c r="O5" t="n">
-        <v>6.452120295921879</v>
+        <v>6.486399174842012</v>
       </c>
       <c r="P5" t="n">
-        <v>358.5682627878573</v>
+        <v>358.6564405437977</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12807,28 +12844,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04468553481281511</v>
+        <v>-0.04588808219446953</v>
       </c>
       <c r="J6" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K6" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004381820979630691</v>
+        <v>0.004647732661685833</v>
       </c>
       <c r="M6" t="n">
-        <v>3.969507349905562</v>
+        <v>3.963840632097755</v>
       </c>
       <c r="N6" t="n">
-        <v>24.25020171714016</v>
+        <v>24.18524718915018</v>
       </c>
       <c r="O6" t="n">
-        <v>4.924449382127931</v>
+        <v>4.917849854270683</v>
       </c>
       <c r="P6" t="n">
-        <v>372.565981215087</v>
+        <v>372.5786030440527</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12866,7 +12903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G316"/>
+  <dimension ref="A1:G317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24561,6 +24598,43 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-36.61353432461184,175.56493883701273</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-36.61414191323246,175.56542677495594</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>-36.61454288522623,175.566178343303</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-36.614836990167525,175.56700498067212</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-36.61482942236787,175.5679175608281</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0142/nzd0142.xlsx
+++ b/data/nzd0142/nzd0142.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G317"/>
+  <dimension ref="A1:G318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8997,6 +8997,33 @@
       <c r="G317" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>361.39</v>
+      </c>
+      <c r="C318" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="D318" t="n">
+        <v>358.17</v>
+      </c>
+      <c r="E318" t="n">
+        <v>355.35</v>
+      </c>
+      <c r="F318" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B335"/>
+  <dimension ref="A1:B336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12364,6 +12391,16 @@
       </c>
       <c r="B335" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -12532,28 +12569,28 @@
         <v>0.0985</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1279518840039161</v>
+        <v>0.1262729313063363</v>
       </c>
       <c r="J2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05927874278549738</v>
+        <v>0.05809368808980664</v>
       </c>
       <c r="M2" t="n">
-        <v>2.955147020259369</v>
+        <v>2.953635928575235</v>
       </c>
       <c r="N2" t="n">
-        <v>13.93382616567677</v>
+        <v>13.91274541801665</v>
       </c>
       <c r="O2" t="n">
-        <v>3.732804062052651</v>
+        <v>3.729979278496952</v>
       </c>
       <c r="P2" t="n">
-        <v>360.7442548823154</v>
+        <v>360.7619653902681</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12610,28 +12647,28 @@
         <v>0.129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1507849586246411</v>
+        <v>0.1459779266226892</v>
       </c>
       <c r="J3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04653269174496755</v>
+        <v>0.0437035286235693</v>
       </c>
       <c r="M3" t="n">
-        <v>4.091319693203132</v>
+        <v>4.09968907001931</v>
       </c>
       <c r="N3" t="n">
-        <v>24.98496344398242</v>
+        <v>25.09365870053387</v>
       </c>
       <c r="O3" t="n">
-        <v>4.998496118232205</v>
+        <v>5.009357114494221</v>
       </c>
       <c r="P3" t="n">
-        <v>364.1329180214547</v>
+        <v>364.1836252144694</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12688,28 +12725,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3009444950726503</v>
+        <v>0.2954574616499911</v>
       </c>
       <c r="J4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1364740136415055</v>
+        <v>0.1320418372899589</v>
       </c>
       <c r="M4" t="n">
-        <v>4.439191909243849</v>
+        <v>4.45107769431159</v>
       </c>
       <c r="N4" t="n">
-        <v>30.73359041425964</v>
+        <v>30.88095432090656</v>
       </c>
       <c r="O4" t="n">
-        <v>5.54378845323842</v>
+        <v>5.557063462018998</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1277706203334</v>
+        <v>359.1856508388815</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12766,28 +12803,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3500573439386048</v>
+        <v>0.3423106035579023</v>
       </c>
       <c r="J5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1350990948578301</v>
+        <v>0.1293973644172578</v>
       </c>
       <c r="M5" t="n">
-        <v>5.301547109153518</v>
+        <v>5.319170394899201</v>
       </c>
       <c r="N5" t="n">
-        <v>42.07337425539114</v>
+        <v>42.42763328378253</v>
       </c>
       <c r="O5" t="n">
-        <v>6.486399174842012</v>
+        <v>6.51364976674234</v>
       </c>
       <c r="P5" t="n">
-        <v>358.6564405437977</v>
+        <v>358.7381573827036</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12844,28 +12881,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04588808219446953</v>
+        <v>-0.048157062106712</v>
       </c>
       <c r="J6" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K6" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004647732661685833</v>
+        <v>0.00514120245210048</v>
       </c>
       <c r="M6" t="n">
-        <v>3.963840632097755</v>
+        <v>3.964189670107349</v>
       </c>
       <c r="N6" t="n">
-        <v>24.18524718915018</v>
+        <v>24.15072998574766</v>
       </c>
       <c r="O6" t="n">
-        <v>4.917849854270683</v>
+        <v>4.914339221680537</v>
       </c>
       <c r="P6" t="n">
-        <v>372.5786030440527</v>
+        <v>372.6025374805844</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12903,7 +12940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G317"/>
+  <dimension ref="A1:G318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24635,6 +24672,43 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-36.61352636864226,175.56495347865052</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-36.61413674466788,175.56543284446118</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-36.61453397082345,175.56618371368228</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-36.614828549523395,175.56700778853693</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-36.61484490342473,175.56791450418353</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0142/nzd0142.xlsx
+++ b/data/nzd0142/nzd0142.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G318"/>
+  <dimension ref="A1:G319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9022,6 +9022,33 @@
         <v>367.72</v>
       </c>
       <c r="G318" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>359.83</v>
+      </c>
+      <c r="C319" t="n">
+        <v>360.55</v>
+      </c>
+      <c r="D319" t="n">
+        <v>359.89</v>
+      </c>
+      <c r="E319" t="n">
+        <v>357.09</v>
+      </c>
+      <c r="F319" t="n">
+        <v>366.08</v>
+      </c>
+      <c r="G319" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9038,7 +9065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B336"/>
+  <dimension ref="A1:B337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12401,6 +12428,16 @@
       </c>
       <c r="B336" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -12569,28 +12606,28 @@
         <v>0.0985</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1262729313063363</v>
+        <v>0.1236357493923831</v>
       </c>
       <c r="J2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05809368808980664</v>
+        <v>0.05596230465292373</v>
       </c>
       <c r="M2" t="n">
-        <v>2.953635928575235</v>
+        <v>2.95654355615927</v>
       </c>
       <c r="N2" t="n">
-        <v>13.91274541801665</v>
+        <v>13.92542589237249</v>
       </c>
       <c r="O2" t="n">
-        <v>3.729979278496952</v>
+        <v>3.731678696293732</v>
       </c>
       <c r="P2" t="n">
-        <v>360.7619653902681</v>
+        <v>360.789893891266</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12647,28 +12684,28 @@
         <v>0.129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1459779266226892</v>
+        <v>0.1413480119339784</v>
       </c>
       <c r="J3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0437035286235693</v>
+        <v>0.04107569305530867</v>
       </c>
       <c r="M3" t="n">
-        <v>4.09968907001931</v>
+        <v>4.107317781086498</v>
       </c>
       <c r="N3" t="n">
-        <v>25.09365870053387</v>
+        <v>25.18868220698047</v>
       </c>
       <c r="O3" t="n">
-        <v>5.009357114494221</v>
+        <v>5.018832753437842</v>
       </c>
       <c r="P3" t="n">
-        <v>364.1836252144694</v>
+        <v>364.2326573181404</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12725,28 +12762,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2954574616499911</v>
+        <v>0.2910810519863407</v>
       </c>
       <c r="J4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1320418372899589</v>
+        <v>0.1288378980478556</v>
       </c>
       <c r="M4" t="n">
-        <v>4.45107769431159</v>
+        <v>4.457517133022459</v>
       </c>
       <c r="N4" t="n">
-        <v>30.88095432090656</v>
+        <v>30.93925312751087</v>
       </c>
       <c r="O4" t="n">
-        <v>5.557063462018998</v>
+        <v>5.562306457532781</v>
       </c>
       <c r="P4" t="n">
-        <v>359.1856508388815</v>
+        <v>359.2319982527676</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12803,28 +12840,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3423106035579023</v>
+        <v>0.3357122542239021</v>
       </c>
       <c r="J5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1293973644172578</v>
+        <v>0.1248906410726011</v>
       </c>
       <c r="M5" t="n">
-        <v>5.319170394899201</v>
+        <v>5.331853525983984</v>
       </c>
       <c r="N5" t="n">
-        <v>42.42763328378253</v>
+        <v>42.64748574892474</v>
       </c>
       <c r="O5" t="n">
-        <v>6.51364976674234</v>
+        <v>6.530504249208076</v>
       </c>
       <c r="P5" t="n">
-        <v>358.7381573827036</v>
+        <v>358.8080357649966</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12881,28 +12918,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.048157062106712</v>
+        <v>-0.05141507364715878</v>
       </c>
       <c r="J6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00514120245210048</v>
+        <v>0.005874022794564282</v>
       </c>
       <c r="M6" t="n">
-        <v>3.964189670107349</v>
+        <v>3.969990689415638</v>
       </c>
       <c r="N6" t="n">
-        <v>24.15072998574766</v>
+        <v>24.16091236086299</v>
       </c>
       <c r="O6" t="n">
-        <v>4.914339221680537</v>
+        <v>4.915375098694198</v>
       </c>
       <c r="P6" t="n">
-        <v>372.6025374805844</v>
+        <v>372.6370407425995</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12940,7 +12977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G318"/>
+  <dimension ref="A1:G319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24709,6 +24746,43 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-36.61353422390338,175.56493902234993</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-36.6141353707456,175.56543445787383</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-36.614520031938696,175.56619211100022</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-36.614813408574,175.56701282532393</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-36.61485949476561,175.56791162320724</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0142/nzd0142.xlsx
+++ b/data/nzd0142/nzd0142.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G319"/>
+  <dimension ref="A1:G321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9049,6 +9049,60 @@
         <v>366.08</v>
       </c>
       <c r="G319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>360.92</v>
+      </c>
+      <c r="C320" t="n">
+        <v>362.43</v>
+      </c>
+      <c r="D320" t="n">
+        <v>362.98</v>
+      </c>
+      <c r="E320" t="n">
+        <v>359.54</v>
+      </c>
+      <c r="F320" t="n">
+        <v>367.59</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="C321" t="n">
+        <v>362.26</v>
+      </c>
+      <c r="D321" t="n">
+        <v>363</v>
+      </c>
+      <c r="E321" t="n">
+        <v>360.47</v>
+      </c>
+      <c r="F321" t="n">
+        <v>369.43</v>
+      </c>
+      <c r="G321" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9065,7 +9119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B337"/>
+  <dimension ref="A1:B339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12438,6 +12492,26 @@
       </c>
       <c r="B337" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -12606,28 +12680,28 @@
         <v>0.0985</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1236357493923831</v>
+        <v>0.1195905283676573</v>
       </c>
       <c r="J2" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K2" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05596230465292373</v>
+        <v>0.05297290718947256</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95654355615927</v>
+        <v>2.957017844955349</v>
       </c>
       <c r="N2" t="n">
-        <v>13.92542589237249</v>
+        <v>13.90509976173382</v>
       </c>
       <c r="O2" t="n">
-        <v>3.731678696293732</v>
+        <v>3.728954245057697</v>
       </c>
       <c r="P2" t="n">
-        <v>360.789893891266</v>
+        <v>360.8329451970461</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12684,28 +12758,28 @@
         <v>0.129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1413480119339784</v>
+        <v>0.1344464630232571</v>
       </c>
       <c r="J3" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K3" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04107569305530867</v>
+        <v>0.03750901683222629</v>
       </c>
       <c r="M3" t="n">
-        <v>4.107317781086498</v>
+        <v>4.111953325162396</v>
       </c>
       <c r="N3" t="n">
-        <v>25.18868220698047</v>
+        <v>25.22503025333243</v>
       </c>
       <c r="O3" t="n">
-        <v>5.018832753437842</v>
+        <v>5.022452613348626</v>
       </c>
       <c r="P3" t="n">
-        <v>364.2326573181404</v>
+        <v>364.306104732524</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12762,28 +12836,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2910810519863407</v>
+        <v>0.2862568914220367</v>
       </c>
       <c r="J4" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K4" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1288378980478556</v>
+        <v>0.1262544717453155</v>
       </c>
       <c r="M4" t="n">
-        <v>4.457517133022459</v>
+        <v>4.451796809228266</v>
       </c>
       <c r="N4" t="n">
-        <v>30.93925312751087</v>
+        <v>30.84054489523268</v>
       </c>
       <c r="O4" t="n">
-        <v>5.562306457532781</v>
+        <v>5.553426410355383</v>
       </c>
       <c r="P4" t="n">
-        <v>359.2319982527676</v>
+        <v>359.2833369424595</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12840,28 +12914,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3357122542239021</v>
+        <v>0.3262982134213959</v>
       </c>
       <c r="J5" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K5" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1248906410726011</v>
+        <v>0.119306213499658</v>
       </c>
       <c r="M5" t="n">
-        <v>5.331853525983984</v>
+        <v>5.340542047353269</v>
       </c>
       <c r="N5" t="n">
-        <v>42.64748574892474</v>
+        <v>42.74282334488534</v>
       </c>
       <c r="O5" t="n">
-        <v>6.530504249208076</v>
+        <v>6.537799579742816</v>
       </c>
       <c r="P5" t="n">
-        <v>358.8080357649966</v>
+        <v>358.9082141298256</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12918,28 +12992,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05141507364715878</v>
+        <v>-0.05481064495451141</v>
       </c>
       <c r="J6" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K6" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005874022794564282</v>
+        <v>0.006744165610440667</v>
       </c>
       <c r="M6" t="n">
-        <v>3.969990689415638</v>
+        <v>3.963940897818612</v>
       </c>
       <c r="N6" t="n">
-        <v>24.16091236086299</v>
+        <v>24.06216316423133</v>
       </c>
       <c r="O6" t="n">
-        <v>4.915375098694198</v>
+        <v>4.905319883986296</v>
       </c>
       <c r="P6" t="n">
-        <v>372.6370407425995</v>
+        <v>372.6731646239565</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12977,7 +13051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G319"/>
+  <dimension ref="A1:G321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24783,6 +24857,80 @@
         </is>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-36.613528735291624,175.56494912322694</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-36.614123070869056,175.565448901756</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-36.614494990568886,175.56620719687226</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-36.614792089420824,175.56701991734852</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-36.61484606005541,175.5679142758135</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-36.61353034662726,175.564946157832</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-36.614124183091995,175.56544759566046</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-36.61449482848882,175.5662072945154</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-36.614783996844224,175.56702260942225</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-36.614829689282644,175.56791750812735</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0142/nzd0142.xlsx
+++ b/data/nzd0142/nzd0142.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G321"/>
+  <dimension ref="A1:G324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9105,6 +9105,87 @@
       <c r="G321" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>359.43</v>
+      </c>
+      <c r="C322" t="n">
+        <v>361.13</v>
+      </c>
+      <c r="D322" t="n">
+        <v>361.99</v>
+      </c>
+      <c r="E322" t="n">
+        <v>359.63</v>
+      </c>
+      <c r="F322" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="C323" t="n">
+        <v>361.88</v>
+      </c>
+      <c r="D323" t="n">
+        <v>362.11</v>
+      </c>
+      <c r="E323" t="n">
+        <v>361.09</v>
+      </c>
+      <c r="F323" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>359.35</v>
+      </c>
+      <c r="C324" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="D324" t="n">
+        <v>360.72</v>
+      </c>
+      <c r="E324" t="n">
+        <v>360.19</v>
+      </c>
+      <c r="F324" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B339"/>
+  <dimension ref="A1:B342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12512,6 +12593,36 @@
       </c>
       <c r="B339" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -12680,28 +12791,28 @@
         <v>0.0985</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1195905283676573</v>
+        <v>0.111693758095904</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K2" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05297290718947256</v>
+        <v>0.04685136454795158</v>
       </c>
       <c r="M2" t="n">
-        <v>2.957017844955349</v>
+        <v>2.966047805320118</v>
       </c>
       <c r="N2" t="n">
-        <v>13.90509976173382</v>
+        <v>13.94840958714252</v>
       </c>
       <c r="O2" t="n">
-        <v>3.728954245057697</v>
+        <v>3.73475696493661</v>
       </c>
       <c r="P2" t="n">
-        <v>360.8329451970461</v>
+        <v>360.9175240494378</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12758,28 +12869,28 @@
         <v>0.129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1344464630232571</v>
+        <v>0.1228281346190767</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03750901683222629</v>
+        <v>0.03165676919894445</v>
       </c>
       <c r="M3" t="n">
-        <v>4.111953325162396</v>
+        <v>4.125352567177525</v>
       </c>
       <c r="N3" t="n">
-        <v>25.22503025333243</v>
+        <v>25.36220110409934</v>
       </c>
       <c r="O3" t="n">
-        <v>5.022452613348626</v>
+        <v>5.036089862591744</v>
       </c>
       <c r="P3" t="n">
-        <v>364.306104732524</v>
+        <v>364.4305410420579</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12836,28 +12947,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2862568914220367</v>
+        <v>0.2766842812760178</v>
       </c>
       <c r="J4" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K4" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1262544717453155</v>
+        <v>0.1201501936423834</v>
       </c>
       <c r="M4" t="n">
-        <v>4.451796809228266</v>
+        <v>4.454005195076636</v>
       </c>
       <c r="N4" t="n">
-        <v>30.84054489523268</v>
+        <v>30.80927936142011</v>
       </c>
       <c r="O4" t="n">
-        <v>5.553426410355383</v>
+        <v>5.550610719679423</v>
       </c>
       <c r="P4" t="n">
-        <v>359.2833369424595</v>
+        <v>359.385876679323</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12914,28 +13025,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3262982134213959</v>
+        <v>0.3131149363439519</v>
       </c>
       <c r="J5" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K5" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L5" t="n">
-        <v>0.119306213499658</v>
+        <v>0.1117529998897309</v>
       </c>
       <c r="M5" t="n">
-        <v>5.340542047353269</v>
+        <v>5.348821570859666</v>
       </c>
       <c r="N5" t="n">
-        <v>42.74282334488534</v>
+        <v>42.82630715879272</v>
       </c>
       <c r="O5" t="n">
-        <v>6.537799579742816</v>
+        <v>6.544181167937874</v>
       </c>
       <c r="P5" t="n">
-        <v>358.9082141298256</v>
+        <v>359.0494082461441</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12992,28 +13103,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05481064495451141</v>
+        <v>-0.05749401304659685</v>
       </c>
       <c r="J6" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K6" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006744165610440667</v>
+        <v>0.007554961243082636</v>
       </c>
       <c r="M6" t="n">
-        <v>3.963940897818612</v>
+        <v>3.941646979110235</v>
       </c>
       <c r="N6" t="n">
-        <v>24.06216316423133</v>
+        <v>23.8642598281035</v>
       </c>
       <c r="O6" t="n">
-        <v>4.905319883986296</v>
+        <v>4.885105917797842</v>
       </c>
       <c r="P6" t="n">
-        <v>372.6731646239565</v>
+        <v>372.7018876708348</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13051,7 +13162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G321"/>
+  <dimension ref="A1:G324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24931,6 +25042,117 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-36.61353623807262,175.5649353156057</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-36.614131576103006,175.56543891396564</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-36.6145030135322,175.56620236353564</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-36.61479130626826,175.56702017787183</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-36.614836895981526,175.56791608520672</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-36.6135324615052,175.56494226575097</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-36.614126669237365,175.56544467615265</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-36.61450204105182,175.56620294939466</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-36.614778601793134,175.56702440413778</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-36.61482203772577,175.56791901888232</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-36.61353664090646,175.56493457425685</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-36.6141298096314,175.56544098835306</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-36.61451330561623,175.5661961631933</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-36.614786433318905,175.5670217989055</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-36.61482203772577,175.56791901888232</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0142/nzd0142.xlsx
+++ b/data/nzd0142/nzd0142.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G324"/>
+  <dimension ref="A1:G327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9184,6 +9184,87 @@
         <v>370.29</v>
       </c>
       <c r="G324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>356.37</v>
+      </c>
+      <c r="C325" t="n">
+        <v>359.57</v>
+      </c>
+      <c r="D325" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="E325" t="n">
+        <v>358.55</v>
+      </c>
+      <c r="F325" t="n">
+        <v>368.58</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="C326" t="n">
+        <v>360.2</v>
+      </c>
+      <c r="D326" t="n">
+        <v>357.38</v>
+      </c>
+      <c r="E326" t="n">
+        <v>358.41</v>
+      </c>
+      <c r="F326" t="n">
+        <v>369.97</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>357.42</v>
+      </c>
+      <c r="C327" t="n">
+        <v>360.06</v>
+      </c>
+      <c r="D327" t="n">
+        <v>356</v>
+      </c>
+      <c r="E327" t="n">
+        <v>357.31</v>
+      </c>
+      <c r="F327" t="n">
+        <v>369.17</v>
+      </c>
+      <c r="G327" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9200,7 +9281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B342"/>
+  <dimension ref="A1:B345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12623,6 +12704,36 @@
       </c>
       <c r="B342" t="n">
         <v>-0.64</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>-0.72</v>
       </c>
     </row>
   </sheetData>
@@ -12791,28 +12902,28 @@
         <v>0.0985</v>
       </c>
       <c r="I2" t="n">
-        <v>0.111693758095904</v>
+        <v>0.09962697837262367</v>
       </c>
       <c r="J2" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K2" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04685136454795158</v>
+        <v>0.03726487741759543</v>
       </c>
       <c r="M2" t="n">
-        <v>2.966047805320118</v>
+        <v>2.996908336059077</v>
       </c>
       <c r="N2" t="n">
-        <v>13.94840958714252</v>
+        <v>14.23592458381079</v>
       </c>
       <c r="O2" t="n">
-        <v>3.73475696493661</v>
+        <v>3.773052422616307</v>
       </c>
       <c r="P2" t="n">
-        <v>360.9175240494378</v>
+        <v>361.047218137463</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12869,28 +12980,28 @@
         <v>0.129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1228281346190767</v>
+        <v>0.1090571258218918</v>
       </c>
       <c r="J3" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K3" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03165676919894445</v>
+        <v>0.0250791112026798</v>
       </c>
       <c r="M3" t="n">
-        <v>4.125352567177525</v>
+        <v>4.14877331362557</v>
       </c>
       <c r="N3" t="n">
-        <v>25.36220110409934</v>
+        <v>25.6678783530922</v>
       </c>
       <c r="O3" t="n">
-        <v>5.036089862591744</v>
+        <v>5.066347634449516</v>
       </c>
       <c r="P3" t="n">
-        <v>364.4305410420579</v>
+        <v>364.5785583838597</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12947,28 +13058,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2766842812760178</v>
+        <v>0.2590634235191374</v>
       </c>
       <c r="J4" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K4" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1201501936423834</v>
+        <v>0.1060428560462537</v>
       </c>
       <c r="M4" t="n">
-        <v>4.454005195076636</v>
+        <v>4.49581974856055</v>
       </c>
       <c r="N4" t="n">
-        <v>30.80927936142011</v>
+        <v>31.41030304044813</v>
       </c>
       <c r="O4" t="n">
-        <v>5.550610719679423</v>
+        <v>5.60448954325442</v>
       </c>
       <c r="P4" t="n">
-        <v>359.385876679323</v>
+        <v>359.5752910739808</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13025,28 +13136,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3131149363439519</v>
+        <v>0.2966094356385645</v>
       </c>
       <c r="J5" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K5" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1117529998897309</v>
+        <v>0.1015587474082016</v>
       </c>
       <c r="M5" t="n">
-        <v>5.348821570859666</v>
+        <v>5.371745584721722</v>
       </c>
       <c r="N5" t="n">
-        <v>42.82630715879272</v>
+        <v>43.20827379210377</v>
       </c>
       <c r="O5" t="n">
-        <v>6.544181167937874</v>
+        <v>6.573300068618789</v>
       </c>
       <c r="P5" t="n">
-        <v>359.0494082461441</v>
+        <v>359.2268344859313</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13103,28 +13214,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05749401304659685</v>
+        <v>-0.06091961342883879</v>
       </c>
       <c r="J6" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K6" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007554961243082636</v>
+        <v>0.008625361342653792</v>
       </c>
       <c r="M6" t="n">
-        <v>3.941646979110235</v>
+        <v>3.923603024425228</v>
       </c>
       <c r="N6" t="n">
-        <v>23.8642598281035</v>
+        <v>23.6809666641799</v>
       </c>
       <c r="O6" t="n">
-        <v>4.885105917797842</v>
+        <v>4.866309347357595</v>
       </c>
       <c r="P6" t="n">
-        <v>372.7018876708348</v>
+        <v>372.7387053106812</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13162,7 +13273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G324"/>
+  <dimension ref="A1:G327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25153,6 +25264,117 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-36.6135516464638,175.56490695900595</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-36.61414178238273,175.5654269286143</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-36.61454256106613,175.56617853858953</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-36.61480070409908,175.5670170515921</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-36.614837251867904,175.56791601493902</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-36.61354600679195,175.56491733789346</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-36.614137660616045,175.56543176885273</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-36.61454037298546,175.56617985677363</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-36.61480192233642,175.56701664633354</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-36.61482488481671,175.56791845674095</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-36.61354635927147,175.56491668921305</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-36.614138576564216,175.56543069324422</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-36.61455155650872,175.56617311938743</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-36.61481149420108,175.56701346215894</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-36.61483200254403,175.5679170513874</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
